--- a/public/downloads/ChenUnderstanding2018.xlsx
+++ b/public/downloads/ChenUnderstanding2018.xlsx
@@ -8,29 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="53">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -62,10 +64,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -165,6 +167,27 @@
   </si>
   <si>
     <t>Adsorbate_name</t>
+  </si>
+  <si>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
   </si>
   <si>
     <t>H</t>
@@ -653,10 +676,10 @@
         <v>2</v>
       </c>
       <c r="N3" s="5">
-        <v>7.022625684738159</v>
+        <v>7022.625684738159</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03546780648857656</v>
+        <v>35.46780648857656</v>
       </c>
       <c r="P3" s="5">
         <v>198</v>
@@ -703,10 +726,10 @@
         <v>2</v>
       </c>
       <c r="N4" s="5">
-        <v>18.834308385849</v>
+        <v>18834.308385849</v>
       </c>
       <c r="O4" s="4">
-        <v>0.07216210109520689</v>
+        <v>72.16210109520689</v>
       </c>
       <c r="P4" s="5">
         <v>261</v>
@@ -753,10 +776,10 @@
         <v>2</v>
       </c>
       <c r="N5" s="5">
-        <v>132.7877745628357</v>
+        <v>132787.7745628357</v>
       </c>
       <c r="O5" s="4">
-        <v>0.4470968840499518</v>
+        <v>447.0968840499518</v>
       </c>
       <c r="P5" s="5">
         <v>297</v>
@@ -803,10 +826,10 @@
         <v>2</v>
       </c>
       <c r="N6" s="5">
-        <v>25.17607140541077</v>
+        <v>25176.07140541077</v>
       </c>
       <c r="O6" s="4">
-        <v>0.09646004369889183</v>
+        <v>96.46004369889182</v>
       </c>
       <c r="P6" s="5">
         <v>261</v>
@@ -853,10 +876,10 @@
         <v>2</v>
       </c>
       <c r="N7" s="5">
-        <v>69.69177937507629</v>
+        <v>69691.77937507629</v>
       </c>
       <c r="O7" s="4">
-        <v>0.3318656160717919</v>
+        <v>331.8656160717919</v>
       </c>
       <c r="P7" s="5">
         <v>210</v>
@@ -887,9 +910,7 @@
       <c r="H8" s="4">
         <v>0.835855767578721</v>
       </c>
-      <c r="I8" s="4">
-        <v>0</v>
-      </c>
+      <c r="I8" s="4"/>
       <c r="J8" s="4">
         <v>0.7044871055761348</v>
       </c>
@@ -903,10 +924,10 @@
         <v>2</v>
       </c>
       <c r="N8" s="5">
-        <v>36.81382822990417</v>
+        <v>36813.82822990417</v>
       </c>
       <c r="O8" s="4">
-        <v>0.05761162477293298</v>
+        <v>57.61162477293298</v>
       </c>
       <c r="P8" s="5">
         <v>639</v>
@@ -937,9 +958,7 @@
       <c r="H9" s="4">
         <v>0.4516615485742363</v>
       </c>
-      <c r="I9" s="4">
-        <v>0</v>
-      </c>
+      <c r="I9" s="4"/>
       <c r="J9" s="4">
         <v>0.2796132182672295</v>
       </c>
@@ -953,10 +972,10 @@
         <v>2</v>
       </c>
       <c r="N9" s="5">
-        <v>21.70182275772095</v>
+        <v>21701.82275772095</v>
       </c>
       <c r="O9" s="4">
-        <v>0.03258531945603746</v>
+        <v>32.58531945603746</v>
       </c>
       <c r="P9" s="5">
         <v>666</v>
@@ -1003,10 +1022,10 @@
         <v>2</v>
       </c>
       <c r="N10" s="5">
-        <v>19.44455456733704</v>
+        <v>19444.55456733704</v>
       </c>
       <c r="O10" s="4">
-        <v>0.08642024252149794</v>
+        <v>86.42024252149794</v>
       </c>
       <c r="P10" s="5">
         <v>225</v>
@@ -1037,9 +1056,7 @@
       <c r="H11" s="4">
         <v>0.3257708167627129</v>
       </c>
-      <c r="I11" s="4">
-        <v>0</v>
-      </c>
+      <c r="I11" s="4"/>
       <c r="J11" s="4">
         <v>0.4414367293908867</v>
       </c>
@@ -1053,10 +1070,10 @@
         <v>2</v>
       </c>
       <c r="N11" s="5">
-        <v>32.76183700561523</v>
+        <v>32761.83700561523</v>
       </c>
       <c r="O11" s="4">
-        <v>0.04451336549675983</v>
+        <v>44.51336549675982</v>
       </c>
       <c r="P11" s="5">
         <v>736</v>
@@ -1103,10 +1120,10 @@
         <v>2</v>
       </c>
       <c r="N12" s="5">
-        <v>5.771361112594604</v>
+        <v>5771.361112594604</v>
       </c>
       <c r="O12" s="4">
-        <v>0.0256504938337538</v>
+        <v>25.6504938337538</v>
       </c>
       <c r="P12" s="5">
         <v>225</v>
@@ -1137,9 +1154,7 @@
       <c r="H13" s="4">
         <v>0.1329934215142998</v>
       </c>
-      <c r="I13" s="4">
-        <v>0</v>
-      </c>
+      <c r="I13" s="4"/>
       <c r="J13" s="4">
         <v>0.2027477836206231</v>
       </c>
@@ -1153,10 +1168,10 @@
         <v>2</v>
       </c>
       <c r="N13" s="5">
-        <v>77.21879720687866</v>
+        <v>77218.79720687866</v>
       </c>
       <c r="O13" s="4">
-        <v>0.078235863431488</v>
+        <v>78.235863431488</v>
       </c>
       <c r="P13" s="5">
         <v>987</v>
@@ -1187,9 +1202,7 @@
       <c r="H14" s="4">
         <v>0.5196630721881945</v>
       </c>
-      <c r="I14" s="4">
-        <v>0</v>
-      </c>
+      <c r="I14" s="4"/>
       <c r="J14" s="4">
         <v>0.5883601820063689</v>
       </c>
@@ -1203,10 +1216,10 @@
         <v>2</v>
       </c>
       <c r="N14" s="5">
-        <v>395.8898029327393</v>
+        <v>395889.8029327393</v>
       </c>
       <c r="O14" s="4">
-        <v>0.4534820193960358</v>
+        <v>453.4820193960358</v>
       </c>
       <c r="P14" s="5">
         <v>873</v>
@@ -1253,10 +1266,10 @@
         <v>2</v>
       </c>
       <c r="N15" s="5">
-        <v>150.4851291179657</v>
+        <v>150485.1291179657</v>
       </c>
       <c r="O15" s="4">
-        <v>0.4688010252896128</v>
+        <v>468.8010252896128</v>
       </c>
       <c r="P15" s="5">
         <v>321</v>
@@ -1287,9 +1300,7 @@
       <c r="H16" s="4">
         <v>0.6315771108462229</v>
       </c>
-      <c r="I16" s="4">
-        <v>0</v>
-      </c>
+      <c r="I16" s="4"/>
       <c r="J16" s="4">
         <v>0.679185471494435</v>
       </c>
@@ -1303,10 +1314,10 @@
         <v>2</v>
       </c>
       <c r="N16" s="5">
-        <v>100.5726647377014</v>
+        <v>100572.6647377014</v>
       </c>
       <c r="O16" s="4">
-        <v>0.1064261002515359</v>
+        <v>106.4261002515359</v>
       </c>
       <c r="P16" s="5">
         <v>945</v>
@@ -1353,10 +1364,10 @@
         <v>2</v>
       </c>
       <c r="N17" s="5">
-        <v>29.95019769668579</v>
+        <v>29950.19769668579</v>
       </c>
       <c r="O17" s="4">
-        <v>0.1073483788411677</v>
+        <v>107.3483788411677</v>
       </c>
       <c r="P17" s="5">
         <v>279</v>
@@ -1384,7 +1395,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1395,9 +1406,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1431,8 +1448,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1454,50 +1479,80 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4572986003995538</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.4572986003995538</v>
-      </c>
+        <v>0.835855767578721</v>
+      </c>
+      <c r="C3" s="4"/>
       <c r="D3" s="4">
-        <v>0.4773311005785672</v>
+        <v>0.7044871055761348</v>
       </c>
       <c r="E3" s="4">
-        <v>93.36734693877551</v>
+        <v>67.95918367346938</v>
       </c>
       <c r="F3" s="4">
-        <v>93.20469798657719</v>
+        <v>64.61409395973155</v>
       </c>
       <c r="G3" s="5">
         <v>2</v>
       </c>
       <c r="H3" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.835855767578721</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1508,6 +1563,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1515,7 +1571,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1526,9 +1582,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1562,8 +1624,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1585,25 +1655,41 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3257708167627129</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
+        <v>0.4516615485742363</v>
+      </c>
+      <c r="C3" s="4"/>
       <c r="D3" s="4">
-        <v>0.4414367293908867</v>
+        <v>0.2796132182672295</v>
       </c>
       <c r="E3" s="4">
-        <v>62.19387755102041</v>
+        <v>69.23469387755102</v>
       </c>
       <c r="F3" s="4">
-        <v>54.42953020134228</v>
+        <v>64.12751677852349</v>
       </c>
       <c r="G3" s="5">
         <v>2</v>
@@ -1626,9 +1712,23 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4516615485742363</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1639,6 +1739,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1646,7 +1747,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1657,9 +1758,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1693,8 +1800,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1716,25 +1831,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1259238338067803</v>
+        <v>0.4572986003995538</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1259238338067803</v>
+        <v>0.4572986003995538</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1574179744317803</v>
+        <v>0.4773311005785672</v>
       </c>
       <c r="E3" s="4">
-        <v>93.82653061224489</v>
+        <v>93.36734693877551</v>
       </c>
       <c r="F3" s="4">
-        <v>93.4284116331096</v>
+        <v>93.20469798657719</v>
       </c>
       <c r="G3" s="5">
         <v>2</v>
@@ -1757,9 +1890,25 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4572986003995538</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4572986003995538</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1770,6 +1919,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1777,7 +1927,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1788,9 +1938,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1824,8 +1980,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1847,25 +2011,41 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1329934215142998</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
+        <v>0.3257708167627129</v>
+      </c>
+      <c r="C3" s="4"/>
       <c r="D3" s="4">
-        <v>0.2027477836206231</v>
+        <v>0.4414367293908867</v>
       </c>
       <c r="E3" s="4">
-        <v>50.93537414965987</v>
+        <v>62.19387755102041</v>
       </c>
       <c r="F3" s="4">
-        <v>52.53355704697987</v>
+        <v>54.42953020134228</v>
       </c>
       <c r="G3" s="5">
         <v>2</v>
@@ -1888,9 +2068,23 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3257708167627129</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1901,6 +2095,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1908,7 +2103,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1919,9 +2114,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1955,8 +2156,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1978,50 +2187,84 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.5196630721881945</v>
+        <v>0.1259238338067803</v>
       </c>
       <c r="C3" s="4">
-        <v>0</v>
+        <v>0.1259238338067803</v>
       </c>
       <c r="D3" s="4">
-        <v>0.5883601820063689</v>
+        <v>0.1574179744317803</v>
       </c>
       <c r="E3" s="4">
-        <v>44.23469387755102</v>
+        <v>93.82653061224489</v>
       </c>
       <c r="F3" s="4">
-        <v>49.41275167785235</v>
+        <v>93.4284116331096</v>
       </c>
       <c r="G3" s="5">
         <v>2</v>
       </c>
       <c r="H3" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1259238338067803</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1259238338067803</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2032,6 +2275,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2039,7 +2283,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2050,9 +2294,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2086,8 +2336,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2109,50 +2367,80 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2404238348797207</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.2404238348797207</v>
-      </c>
+        <v>0.1329934215142998</v>
+      </c>
+      <c r="C3" s="4"/>
       <c r="D3" s="4">
-        <v>0.2737461542676556</v>
+        <v>0.2027477836206231</v>
       </c>
       <c r="E3" s="4">
-        <v>89.84693877551021</v>
+        <v>50.93537414965987</v>
       </c>
       <c r="F3" s="4">
-        <v>89.12751677852349</v>
+        <v>52.53355704697987</v>
       </c>
       <c r="G3" s="5">
         <v>2</v>
       </c>
       <c r="H3" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1329934215142998</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2163,6 +2451,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2170,7 +2459,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2181,9 +2470,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2217,8 +2512,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2240,25 +2543,41 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.6315771108462229</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
+        <v>0.5196630721881945</v>
+      </c>
+      <c r="C3" s="4"/>
       <c r="D3" s="4">
-        <v>0.679185471494435</v>
+        <v>0.5883601820063689</v>
       </c>
       <c r="E3" s="4">
-        <v>35.88435374149644</v>
+        <v>44.23469387755102</v>
       </c>
       <c r="F3" s="4">
-        <v>40.32997762863493</v>
+        <v>49.41275167785235</v>
       </c>
       <c r="G3" s="5">
         <v>2</v>
@@ -2281,9 +2600,23 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.5196630721881945</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2294,6 +2627,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2301,7 +2635,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2312,9 +2646,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2348,8 +2688,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2371,25 +2719,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2933505987724629</v>
+        <v>0.2404238348797207</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2933505987724629</v>
+        <v>0.2404238348797207</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3054790711002227</v>
+        <v>0.2737461542676556</v>
       </c>
       <c r="E3" s="4">
-        <v>91.22448979591837</v>
+        <v>89.84693877551021</v>
       </c>
       <c r="F3" s="4">
-        <v>88.8255033557047</v>
+        <v>89.12751677852349</v>
       </c>
       <c r="G3" s="5">
         <v>2</v>
@@ -2412,9 +2778,25 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2404238348797207</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2404238348797207</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2425,12 +2807,1214 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.6315771108462229</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4">
+        <v>0.679185471494435</v>
+      </c>
+      <c r="E3" s="4">
+        <v>35.88435374149644</v>
+      </c>
+      <c r="F3" s="4">
+        <v>40.32997762863493</v>
+      </c>
+      <c r="G3" s="5">
+        <v>2</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>2</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>2</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.6315771108462229</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.2933505987724629</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.2933505987724629</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.3054790711002227</v>
+      </c>
+      <c r="E3" s="4">
+        <v>91.22448979591837</v>
+      </c>
+      <c r="F3" s="4">
+        <v>88.8255033557047</v>
+      </c>
+      <c r="G3" s="5">
+        <v>2</v>
+      </c>
+      <c r="H3" s="5">
+        <v>2</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2933505987724629</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2933505987724629</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>100</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.5060505485132012</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.5060505485132012</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.5181064223840508</v>
+      </c>
+      <c r="K3" s="4">
+        <v>93.9795918367347</v>
+      </c>
+      <c r="L3" s="4">
+        <v>94.59731543624162</v>
+      </c>
+      <c r="M3" s="5">
+        <v>2</v>
+      </c>
+      <c r="N3" s="5">
+        <v>7022.625684738159</v>
+      </c>
+      <c r="O3" s="4">
+        <v>35.46780648857656</v>
+      </c>
+      <c r="P3" s="5">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>100</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.5465941047265801</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.5465941047265801</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.6255888557031426</v>
+      </c>
+      <c r="K4" s="4">
+        <v>90.45918367346938</v>
+      </c>
+      <c r="L4" s="4">
+        <v>91.89597315436242</v>
+      </c>
+      <c r="M4" s="5">
+        <v>2</v>
+      </c>
+      <c r="N4" s="5">
+        <v>18834.308385849</v>
+      </c>
+      <c r="O4" s="4">
+        <v>72.16210109520689</v>
+      </c>
+      <c r="P4" s="5">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>100</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.345257258971003</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.345257258971003</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.3384323483302865</v>
+      </c>
+      <c r="K5" s="4">
+        <v>90.27210884353741</v>
+      </c>
+      <c r="L5" s="4">
+        <v>88.62416107382552</v>
+      </c>
+      <c r="M5" s="5">
+        <v>2</v>
+      </c>
+      <c r="N5" s="5">
+        <v>132787.7745628357</v>
+      </c>
+      <c r="O5" s="4">
+        <v>447.0968840499518</v>
+      </c>
+      <c r="P5" s="5">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>100</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.5275337314203057</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.5275337314203057</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.5518409823968682</v>
+      </c>
+      <c r="K6" s="4">
+        <v>91.93877551020408</v>
+      </c>
+      <c r="L6" s="4">
+        <v>92.4496644295302</v>
+      </c>
+      <c r="M6" s="5">
+        <v>2</v>
+      </c>
+      <c r="N6" s="5">
+        <v>25176.07140541077</v>
+      </c>
+      <c r="O6" s="4">
+        <v>96.46004369889182</v>
+      </c>
+      <c r="P6" s="5">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>100</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.3268506145074639</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.3268506145074639</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.3397137736871514</v>
+      </c>
+      <c r="K7" s="4">
+        <v>95.45918367346938</v>
+      </c>
+      <c r="L7" s="4">
+        <v>95.60402684563758</v>
+      </c>
+      <c r="M7" s="5">
+        <v>2</v>
+      </c>
+      <c r="N7" s="5">
+        <v>69691.77937507629</v>
+      </c>
+      <c r="O7" s="4">
+        <v>331.8656160717919</v>
+      </c>
+      <c r="P7" s="5">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3">
+        <v>100</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>100</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.835855767578721</v>
+      </c>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4">
+        <v>0.7044871055761348</v>
+      </c>
+      <c r="K8" s="4">
+        <v>67.95918367346938</v>
+      </c>
+      <c r="L8" s="4">
+        <v>64.61409395973155</v>
+      </c>
+      <c r="M8" s="5">
+        <v>2</v>
+      </c>
+      <c r="N8" s="5">
+        <v>36813.82822990417</v>
+      </c>
+      <c r="O8" s="4">
+        <v>57.61162477293298</v>
+      </c>
+      <c r="P8" s="5">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3">
+        <v>100</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>100</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.4516615485742363</v>
+      </c>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4">
+        <v>0.2796132182672295</v>
+      </c>
+      <c r="K9" s="4">
+        <v>69.23469387755102</v>
+      </c>
+      <c r="L9" s="4">
+        <v>64.12751677852349</v>
+      </c>
+      <c r="M9" s="5">
+        <v>2</v>
+      </c>
+      <c r="N9" s="5">
+        <v>21701.82275772095</v>
+      </c>
+      <c r="O9" s="4">
+        <v>32.58531945603746</v>
+      </c>
+      <c r="P9" s="5">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>100</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.4572986003995538</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.4572986003995538</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.4773311005785672</v>
+      </c>
+      <c r="K10" s="4">
+        <v>93.36734693877551</v>
+      </c>
+      <c r="L10" s="4">
+        <v>93.20469798657719</v>
+      </c>
+      <c r="M10" s="5">
+        <v>2</v>
+      </c>
+      <c r="N10" s="5">
+        <v>19444.55456733704</v>
+      </c>
+      <c r="O10" s="4">
+        <v>86.42024252149794</v>
+      </c>
+      <c r="P10" s="5">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3">
+        <v>100</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>100</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.3257708167627129</v>
+      </c>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4">
+        <v>0.4414367293908867</v>
+      </c>
+      <c r="K11" s="4">
+        <v>62.19387755102041</v>
+      </c>
+      <c r="L11" s="4">
+        <v>54.42953020134228</v>
+      </c>
+      <c r="M11" s="5">
+        <v>2</v>
+      </c>
+      <c r="N11" s="5">
+        <v>32761.83700561523</v>
+      </c>
+      <c r="O11" s="4">
+        <v>44.51336549675982</v>
+      </c>
+      <c r="P11" s="5">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>100</v>
+      </c>
+      <c r="C12" s="3">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.1259238338067803</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.1259238338067803</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.1574179744317803</v>
+      </c>
+      <c r="K12" s="4">
+        <v>93.82653061224489</v>
+      </c>
+      <c r="L12" s="4">
+        <v>93.4284116331096</v>
+      </c>
+      <c r="M12" s="5">
+        <v>2</v>
+      </c>
+      <c r="N12" s="5">
+        <v>5771.361112594604</v>
+      </c>
+      <c r="O12" s="4">
+        <v>25.6504938337538</v>
+      </c>
+      <c r="P12" s="5">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3">
+        <v>100</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>100</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.1329934215142998</v>
+      </c>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4">
+        <v>0.2027477836206231</v>
+      </c>
+      <c r="K13" s="4">
+        <v>50.93537414965987</v>
+      </c>
+      <c r="L13" s="4">
+        <v>52.53355704697987</v>
+      </c>
+      <c r="M13" s="5">
+        <v>2</v>
+      </c>
+      <c r="N13" s="5">
+        <v>77218.79720687866</v>
+      </c>
+      <c r="O13" s="4">
+        <v>78.235863431488</v>
+      </c>
+      <c r="P13" s="5">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3">
+        <v>100</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>100</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.5196630721881945</v>
+      </c>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4">
+        <v>0.5883601820063689</v>
+      </c>
+      <c r="K14" s="4">
+        <v>44.23469387755102</v>
+      </c>
+      <c r="L14" s="4">
+        <v>49.41275167785235</v>
+      </c>
+      <c r="M14" s="5">
+        <v>2</v>
+      </c>
+      <c r="N14" s="5">
+        <v>395889.8029327393</v>
+      </c>
+      <c r="O14" s="4">
+        <v>453.4820193960358</v>
+      </c>
+      <c r="P14" s="5">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>100</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.2404238348797207</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.2404238348797207</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.2737461542676556</v>
+      </c>
+      <c r="K15" s="4">
+        <v>89.84693877551021</v>
+      </c>
+      <c r="L15" s="4">
+        <v>89.12751677852349</v>
+      </c>
+      <c r="M15" s="5">
+        <v>2</v>
+      </c>
+      <c r="N15" s="5">
+        <v>150485.1291179657</v>
+      </c>
+      <c r="O15" s="4">
+        <v>468.8010252896128</v>
+      </c>
+      <c r="P15" s="5">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>0</v>
+      </c>
+      <c r="C16" s="3">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3">
+        <v>100</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>100</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.6315771108462229</v>
+      </c>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4">
+        <v>0.679185471494435</v>
+      </c>
+      <c r="K16" s="4">
+        <v>35.88435374149644</v>
+      </c>
+      <c r="L16" s="4">
+        <v>40.32997762863493</v>
+      </c>
+      <c r="M16" s="5">
+        <v>2</v>
+      </c>
+      <c r="N16" s="5">
+        <v>100572.6647377014</v>
+      </c>
+      <c r="O16" s="4">
+        <v>106.4261002515359</v>
+      </c>
+      <c r="P16" s="5">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>100</v>
+      </c>
+      <c r="C17" s="3">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.2933505987724629</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.2933505987724629</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0.3054790711002227</v>
+      </c>
+      <c r="K17" s="4">
+        <v>91.22448979591837</v>
+      </c>
+      <c r="L17" s="4">
+        <v>88.8255033557047</v>
+      </c>
+      <c r="M17" s="5">
+        <v>2</v>
+      </c>
+      <c r="N17" s="5">
+        <v>29950.19769668579</v>
+      </c>
+      <c r="O17" s="4">
+        <v>107.3483788411677</v>
+      </c>
+      <c r="P17" s="5">
+        <v>279</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3185,9 +4769,764 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>2</v>
+      </c>
+      <c r="C3" s="5">
+        <v>0</v>
+      </c>
+      <c r="D3" s="5">
+        <v>0</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5">
+        <v>0</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>2</v>
+      </c>
+      <c r="C4" s="5">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>2</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>2</v>
+      </c>
+      <c r="C6" s="5">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>2</v>
+      </c>
+      <c r="C7" s="5">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>0</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5">
+        <v>2</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>2</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>1</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5">
+        <v>0</v>
+      </c>
+      <c r="D9" s="5">
+        <v>2</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5">
+        <v>2</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>1</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>2</v>
+      </c>
+      <c r="C10" s="5">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>0</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5">
+        <v>2</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>2</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>1</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>2</v>
+      </c>
+      <c r="C12" s="5">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5">
+        <v>0</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
+        <v>0</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>0</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5">
+        <v>2</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>2</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>1</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5">
+        <v>0</v>
+      </c>
+      <c r="D14" s="5">
+        <v>2</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5">
+        <v>2</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>1</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>2</v>
+      </c>
+      <c r="C15" s="5">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5">
+        <v>0</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5">
+        <v>0</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>0</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5">
+        <v>0</v>
+      </c>
+      <c r="D16" s="5">
+        <v>2</v>
+      </c>
+      <c r="E16" s="5">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5">
+        <v>2</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>1</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>2</v>
+      </c>
+      <c r="C17" s="5">
+        <v>0</v>
+      </c>
+      <c r="D17" s="5">
+        <v>0</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>0</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>0</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3198,9 +5537,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3234,8 +5579,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3257,10 +5610,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.5060505485132012</v>
@@ -3298,9 +5669,25 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.5060505485132012</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.5060505485132012</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3311,14 +5698,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3329,9 +5717,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3365,8 +5759,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3388,10 +5790,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.5465941047265801</v>
@@ -3429,9 +5849,25 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.5465941047265801</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.5465941047265801</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3442,14 +5878,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3460,9 +5897,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3496,8 +5939,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3519,10 +5970,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.345257258971003</v>
@@ -3560,9 +6029,25 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.345257258971003</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.345257258971003</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3573,14 +6058,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3591,9 +6077,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3627,8 +6119,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3650,10 +6150,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.5275337314203057</v>
@@ -3691,9 +6209,25 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.5275337314203057</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.5275337314203057</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3704,14 +6238,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3722,9 +6257,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3758,8 +6299,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3781,10 +6330,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.3268506145074639</v>
@@ -3822,9 +6389,25 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3268506145074639</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3268506145074639</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3835,268 +6418,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.835855767578721</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.7044871055761348</v>
-      </c>
-      <c r="E3" s="4">
-        <v>67.95918367346938</v>
-      </c>
-      <c r="F3" s="4">
-        <v>64.61409395973155</v>
-      </c>
-      <c r="G3" s="5">
-        <v>2</v>
-      </c>
-      <c r="H3" s="5">
-        <v>0</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>2</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>2</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.4516615485742363</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.2796132182672295</v>
-      </c>
-      <c r="E3" s="4">
-        <v>69.23469387755102</v>
-      </c>
-      <c r="F3" s="4">
-        <v>64.12751677852349</v>
-      </c>
-      <c r="G3" s="5">
-        <v>2</v>
-      </c>
-      <c r="H3" s="5">
-        <v>0</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>2</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>2</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
